--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484025_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484025_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8963</v>
+        <v>5.5874</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8713</v>
+        <v>3.1977</v>
       </c>
       <c r="F2" t="n">
-        <v>2.025</v>
+        <v>2.3897</v>
       </c>
       <c r="G2" t="n">
         <v>3.7684</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0945</v>
+        <v>0.5966</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7368</v>
+        <v>0.5896</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3578</v>
+        <v>0.007</v>
       </c>
       <c r="V2" t="n">
         <v>2.2144</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0581</v>
+        <v>2.1756</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3387</v>
+        <v>-1.0529</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3968</v>
+        <v>3.2285</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9892</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8489</v>
+        <v>0.9664</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3548</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4941</v>
+        <v>0.3258</v>
       </c>
       <c r="V3" t="n">
         <v>1.2065</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MASIP</t>
+          <t>J. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4742</v>
+        <v>1.7649</v>
       </c>
       <c r="E4" t="n">
-        <v>1.147</v>
+        <v>0.7811</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3272</v>
+        <v>0.9838</v>
       </c>
       <c r="G4" t="n">
-        <v>1.013</v>
+        <v>2.4712</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.718</v>
+        <v>2.5852</v>
       </c>
       <c r="I4" t="n">
-        <v>2.731</v>
+        <v>-0.114</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2981</v>
+        <v>3.3091</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.0703</v>
+        <v>3.3065</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7722</v>
+        <v>0.0026</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3111</v>
+        <v>-0.8379</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3523</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9588</v>
+        <v>-0.1165</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7935</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0806</v>
+        <v>0.3372</v>
       </c>
       <c r="T4" t="n">
-        <v>2.171</v>
+        <v>0.4478</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9096</v>
+        <v>-0.1106</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.4129</v>
+        <v>0.742</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.6789</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8243</v>
+        <v>1.3601</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1362</v>
+        <v>1.7281</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3119</v>
+        <v>-0.368</v>
       </c>
       <c r="G5" t="n">
         <v>-2.6248</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2266</v>
+        <v>0.7624</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4171</v>
+        <v>1.009</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1905</v>
+        <v>-0.2467</v>
       </c>
       <c r="V5" t="n">
         <v>3.4209</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CAMPENY LLOVERAS</t>
+          <t>I. FERNANDEZ MASIP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6169</v>
+        <v>0.9311</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.0247</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0399</v>
+        <v>0.9064</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4712</v>
+        <v>1.013</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5852</v>
+        <v>-1.718</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.114</v>
+        <v>2.731</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3091</v>
+        <v>-0.2981</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3065</v>
+        <v>-2.0703</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0026</v>
+        <v>1.7722</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8379</v>
+        <v>1.3111</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7213000000000001</v>
+        <v>0.3523</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1165</v>
+        <v>0.9588</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1893</v>
+        <v>1.5375</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2438</v>
+        <v>1.0487</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0545</v>
+        <v>0.4888</v>
       </c>
       <c r="V6" t="n">
-        <v>0.742</v>
+        <v>-2.4129</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X6" t="n">
-        <v>0.742</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5748</v>
+        <v>-0.6768</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1791</v>
+        <v>1.4596</v>
       </c>
       <c r="G7" t="n">
         <v>1.103</v>
@@ -1000,13 +1000,13 @@
         <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2948</v>
+        <v>0.4733</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7483</v>
+        <v>0.6463</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4535</v>
+        <v>-0.173</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3825</v>
+        <v>0.472</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3219</v>
+        <v>-0.6077</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9394</v>
+        <v>1.0797</v>
       </c>
       <c r="G8" t="n">
         <v>0.0876</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6604</v>
+        <v>0.1941</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5611</v>
+        <v>0.1531</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0993</v>
+        <v>0.041</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6032</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4392</v>
+        <v>-0.4111</v>
       </c>
       <c r="E9" t="n">
         <v>-0.187</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2521</v>
+        <v>-0.2241</v>
       </c>
       <c r="G9" t="n">
         <v>0.0065</v>
@@ -1156,13 +1156,13 @@
         <v>0.3968</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5764</v>
+        <v>-0.5484</v>
       </c>
       <c r="T9" t="n">
         <v>-0.187</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3894</v>
+        <v>-0.3614</v>
       </c>
       <c r="V9" t="n">
         <v>-0.266</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4133</v>
+        <v>-1.449</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0745</v>
+        <v>-0.1295</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4878</v>
+        <v>-1.3195</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3335</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5317</v>
+        <v>0.496</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6915</v>
+        <v>0.4875</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1599</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0082</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.316</v>
+        <v>-3.2904</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7584</v>
+        <v>-2.4523</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5576</v>
+        <v>-0.8381</v>
       </c>
       <c r="G11" t="n">
         <v>-3.551</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3741</v>
+        <v>0.3996</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1304</v>
+        <v>0.4365</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2436</v>
+        <v>-0.0369</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5358000000000001</v>
@@ -1345,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.923100000000001</v>
+        <v>7.923400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6252999999999993</v>
+        <v>0.6254</v>
       </c>
       <c r="F12" t="n">
-        <v>7.297999999999999</v>
+        <v>7.298000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9512000000000009</v>
+        <v>0.9512</v>
       </c>
       <c r="H12" t="n">
         <v>1.6638</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7127000000000006</v>
+        <v>-0.7127000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.05440000000000067</v>
+        <v>-0.05439999999999978</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1892</v>
+        <v>4.189200000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.2436</v>
+        <v>-4.243599999999999</v>
       </c>
       <c r="M12" t="n">
         <v>1.0057</v>
@@ -1381,7 +1381,7 @@
         <v>3.5311</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.33066907387547e-16</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.8949</v>
@@ -1393,13 +1393,13 @@
         <v>5.214700000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>5.272</v>
+        <v>5.272099999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.05760000000000007</v>
+        <v>-0.05750000000000002</v>
       </c>
       <c r="V12" t="n">
-        <v>1.757699999999999</v>
+        <v>1.7577</v>
       </c>
       <c r="W12" t="n">
         <v>8.3027</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8709</v>
+        <v>5.5929</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5242</v>
+        <v>4.2181</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3467</v>
+        <v>1.3748</v>
       </c>
       <c r="G13" t="n">
         <v>2.3538</v>
@@ -1468,13 +1468,13 @@
         <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0527</v>
+        <v>-0.2253</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3061</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2534</v>
+        <v>-0.2253</v>
       </c>
       <c r="V13" t="n">
         <v>2.0757</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2733</v>
+        <v>2.5955</v>
       </c>
       <c r="E14" t="n">
-        <v>1.694</v>
+        <v>1.796</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5793</v>
+        <v>0.7995</v>
       </c>
       <c r="G14" t="n">
         <v>2.807</v>
@@ -1546,13 +1546,13 @@
         <v>0.7935</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6014</v>
+        <v>-0.2792</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1191</v>
+        <v>0.2211</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7205</v>
+        <v>-0.5003</v>
       </c>
       <c r="V14" t="n">
         <v>0.266</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0894</v>
+        <v>1.8138</v>
       </c>
       <c r="E15" t="n">
-        <v>1.489</v>
+        <v>2.1011</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3995</v>
+        <v>-0.2873</v>
       </c>
       <c r="G15" t="n">
         <v>1.802</v>
@@ -1624,13 +1624,13 @@
         <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0418</v>
+        <v>-0.3174</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7481</v>
+        <v>-0.136</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2937</v>
+        <v>-0.1814</v>
       </c>
       <c r="V15" t="n">
         <v>-0.266</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5109</v>
+        <v>0.6891</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1643</v>
+        <v>-0.2201</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6533</v>
+        <v>0.9093</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8502999999999999</v>
+        <v>1.5044</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4486</v>
+        <v>0.5289</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4016</v>
+        <v>0.9755</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0202</v>
+        <v>1.7276</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0202</v>
+        <v>1.3158</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.4118</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8704</v>
+        <v>-0.2233</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4688</v>
+        <v>-0.7869</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4016</v>
+        <v>0.5637</v>
       </c>
       <c r="P16" t="n">
         <v>0.1984</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1984</v>
+        <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0436</v>
+        <v>-0.9423</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0623</v>
+        <v>-0.1586</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0187</v>
+        <v>-0.7837</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2065</v>
+        <v>-0.0713</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>0.1947</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.133</v>
+        <v>0.641</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9343</v>
+        <v>1.2663</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8013</v>
+        <v>-0.6253</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5044</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5289</v>
+        <v>-0.4486</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9755</v>
+        <v>-0.4016</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7276</v>
+        <v>0.0202</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3158</v>
+        <v>0.0202</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4118</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2233</v>
+        <v>-0.8704</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7869</v>
+        <v>-0.4688</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5637</v>
+        <v>-0.4016</v>
       </c>
       <c r="P17" t="n">
         <v>0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1822</v>
+        <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7645</v>
+        <v>0.0864</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8728</v>
+        <v>0.0397</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8917</v>
+        <v>0.0468</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0713</v>
+        <v>1.2065</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1947</v>
+        <v>1.2065</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. SEVILLANO PUIG</t>
+          <t>A. TARRIDA TORRES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6126</v>
+        <v>-1.1411</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6967</v>
+        <v>-2.0046</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0841</v>
+        <v>0.8635</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.514</v>
+        <v>0.1875</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1305</v>
+        <v>-0.7557</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.6445</v>
+        <v>0.9432</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.3677</v>
+        <v>-0.2467</v>
       </c>
       <c r="K18" t="n">
-        <v>0.711</v>
+        <v>-0.3672</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.0786</v>
+        <v>0.1205</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1463</v>
+        <v>0.4342</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5804</v>
+        <v>-0.3886</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4341</v>
+        <v>0.8227</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0403</v>
+        <v>-0.3528</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7937</v>
+        <v>0.0114</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7534</v>
+        <v>-0.3642</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8692</v>
+        <v>1.2065</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8692</v>
+        <v>1.2065</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. TARRIDA TORRES</t>
+          <t>G. SEVILLANO PUIG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7354</v>
+        <v>-2.2749</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5147</v>
+        <v>-3.4109</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7793</v>
+        <v>1.136</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1875</v>
+        <v>-3.514</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7557</v>
+        <v>0.1305</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9432</v>
+        <v>-3.6445</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2467</v>
+        <v>-3.3677</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3672</v>
+        <v>0.711</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1205</v>
+        <v>-4.0786</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4342</v>
+        <v>-0.1463</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3886</v>
+        <v>-0.5804</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8227</v>
+        <v>0.4341</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1822</v>
+        <v>0.9919</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9472</v>
+        <v>-0.6221</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4988</v>
+        <v>0.0795</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4484</v>
+        <v>-0.7015</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2065</v>
+        <v>0.8692</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2065</v>
+        <v>0.8692</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. BARBECHO GARCIA</t>
+          <t>V. CASTELLON MARTIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1766</v>
+        <v>-3.3266</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6541</v>
+        <v>-3.7395</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5225</v>
+        <v>0.4129</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0533</v>
+        <v>-3.3621</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6883</v>
+        <v>-2.1974</v>
       </c>
       <c r="I20" t="n">
-        <v>1.635</v>
+        <v>-1.1647</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2744</v>
+        <v>-2.5947</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-1.2744</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6827</v>
+        <v>-1.3202</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2212</v>
+        <v>-0.7674</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7311</v>
+        <v>-0.923</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9523</v>
+        <v>0.1555</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2896</v>
+        <v>-0.5597</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6042</v>
+        <v>-0.153</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3146</v>
+        <v>-0.4068</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.6194</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.6194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3271</v>
+        <v>-3.5814</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4732</v>
+        <v>-1.7793</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8539</v>
+        <v>-1.802</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1755</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6513</v>
+        <v>-0.9055</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2382</v>
+        <v>-0.0679</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8894</v>
+        <v>-0.8376</v>
       </c>
       <c r="V21" t="n">
         <v>-3.6907</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. CASTELLON MARTIN</t>
+          <t>N. BAQUES GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.569</v>
+        <v>-4.0928</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8416</v>
+        <v>-3.7486</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2726</v>
+        <v>-0.3441</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3621</v>
+        <v>-1.6508</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1974</v>
+        <v>0.277</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1647</v>
+        <v>-1.9278</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5947</v>
+        <v>-1.9847</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2744</v>
+        <v>-0.0244</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3202</v>
+        <v>-1.9603</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7674</v>
+        <v>0.3339</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.923</v>
+        <v>0.3014</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1555</v>
+        <v>0.0325</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5952</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.802</v>
+        <v>-0.7241</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.255</v>
+        <v>-0.2606</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.547</v>
+        <v>-0.4635</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. BAQUES GARCIA</t>
+          <t>P. BARBECHO GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1141</v>
+        <v>-4.1587</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0547</v>
+        <v>-1.7764</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0594</v>
+        <v>-2.3823</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6508</v>
+        <v>-0.0533</v>
       </c>
       <c r="H23" t="n">
-        <v>0.277</v>
+        <v>-1.6883</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9278</v>
+        <v>1.635</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9847</v>
+        <v>-0.2744</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0244</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9603</v>
+        <v>0.6827</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3339</v>
+        <v>0.2212</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3014</v>
+        <v>-0.7311</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0325</v>
+        <v>0.9523</v>
       </c>
       <c r="P23" t="n">
+        <v>-0.7935</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.9838</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-2.9758</v>
-      </c>
       <c r="R23" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7454</v>
+        <v>0.3075</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5667</v>
+        <v>0.4818</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1787</v>
+        <v>-0.1743</v>
       </c>
       <c r="V23" t="n">
-        <v>0.266</v>
+        <v>-3.6194</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2065</v>
+        <v>-3.6194</v>
       </c>
     </row>
     <row r="24">
@@ -2281,34 +2281,34 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.923300000000001</v>
+        <v>-7.2432</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.297799999999999</v>
+        <v>-7.297899999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6252999999999996</v>
+        <v>0.05500000000000016</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9512999999999996</v>
+        <v>-0.951299999999999</v>
       </c>
       <c r="H24" t="n">
         <v>-1.6638</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7127000000000003</v>
+        <v>0.7127000000000006</v>
       </c>
       <c r="J24" t="n">
         <v>-1.0057</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5254</v>
+        <v>2.525399999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.531099999999999</v>
+        <v>-3.5311</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0545000000000001</v>
+        <v>0.05450000000000027</v>
       </c>
       <c r="N24" t="n">
         <v>-4.1892</v>
@@ -2317,7 +2317,7 @@
         <v>4.2437</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0002000000000002</v>
+        <v>0.000199999999999867</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.8949</v>
@@ -2326,22 +2326,22 @@
         <v>12.8949</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.214600000000001</v>
+        <v>-4.5345</v>
       </c>
       <c r="T24" t="n">
-        <v>0.05759999999999998</v>
+        <v>0.05740000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.2721</v>
+        <v>-4.5918</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.757500000000001</v>
+        <v>-1.7575</v>
       </c>
       <c r="W24" t="n">
         <v>6.545199999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.302800000000001</v>
+        <v>-8.3028</v>
       </c>
     </row>
   </sheetData>
